--- a/बजेट माग estimate/नगर बजेट estimate/छापभन्ज्याङ बज्रयोगिनी मन्दिर पूर्वाधार विकास/छापभन्ज्याङ बज्रयोगिनी मन्दिर पूर्वाधार विकास.xlsx
+++ b/बजेट माग estimate/नगर बजेट estimate/छापभन्ज्याङ बज्रयोगिनी मन्दिर पूर्वाधार विकास/छापभन्ज्याङ बज्रयोगिनी मन्दिर पूर्वाधार विकास.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DF037EC-722E-4B06-B39B-014396E76060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11040"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="estimate" sheetId="12" r:id="rId1"/>
+    <sheet name="for upabhokta" sheetId="13" r:id="rId2"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
     <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
     <definedName name="description_103">[1]Abstract!$B$16</definedName>
     <definedName name="description_124" localSheetId="0">#REF!</definedName>
+    <definedName name="description_124" localSheetId="1">#REF!</definedName>
     <definedName name="description_124">#REF!</definedName>
     <definedName name="description_247">[1]Abstract!$B$22</definedName>
     <definedName name="description_248">[1]Abstract!$B$23</definedName>
@@ -25,21 +28,27 @@
     <definedName name="description_276">[3]Abstract!$B$40</definedName>
     <definedName name="description_3">[1]Abstract!$B$169</definedName>
     <definedName name="description_310" localSheetId="0">#REF!</definedName>
+    <definedName name="description_310" localSheetId="1">#REF!</definedName>
     <definedName name="description_310">#REF!</definedName>
     <definedName name="description_312" localSheetId="0">#REF!</definedName>
+    <definedName name="description_312" localSheetId="1">#REF!</definedName>
     <definedName name="description_312">#REF!</definedName>
     <definedName name="description_5">[1]Abstract!$B$171</definedName>
     <definedName name="description_6" localSheetId="0">#REF!</definedName>
+    <definedName name="description_6" localSheetId="1">#REF!</definedName>
     <definedName name="description_6">#REF!</definedName>
     <definedName name="description_759">[1]Abstract!$B$278</definedName>
     <definedName name="description_781" localSheetId="0">#REF!</definedName>
+    <definedName name="description_781" localSheetId="1">#REF!</definedName>
     <definedName name="description_781">#REF!</definedName>
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$60</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'for upabhokta'!$A$1:$K$60</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'for upabhokta'!$1:$8</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -48,6 +57,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -55,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="44">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -194,14 +205,17 @@
       <t>5fke~Hofª ah|of]lugL dlGb/ k"jf{wf/ ljsf;</t>
     </r>
   </si>
+  <si>
+    <t>-for steps</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="14" x14ac:knownFonts="1">
     <font>
@@ -361,9 +375,9 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
@@ -375,7 +389,7 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -399,14 +413,14 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -425,7 +439,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -440,7 +454,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -457,7 +471,24 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -477,32 +508,15 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="3"/>
+    <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 3" xfId="5"/>
-    <cellStyle name="Percent 2" xfId="4"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Percent 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -518,7 +532,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -612,7 +626,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -671,7 +685,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -735,9 +749,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -775,9 +789,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -812,7 +826,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -847,7 +861,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1020,135 +1034,135 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S51"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S60"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="19" customWidth="1"/>
-    <col min="2" max="2" width="30.88671875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" style="19" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" style="19" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" style="19" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" style="19"/>
+    <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="19" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="19" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="19"/>
     <col min="8" max="8" width="5" style="19" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" style="19" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.109375" style="19"/>
+    <col min="9" max="9" width="9.5703125" style="19" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.140625" style="19"/>
     <col min="13" max="16" width="0" style="19" hidden="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.109375" style="19"/>
+    <col min="17" max="16384" width="9.140625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
-      <c r="J1" s="47"/>
-      <c r="K1" s="47"/>
-    </row>
-    <row r="2" spans="1:16" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+    </row>
+    <row r="2" spans="1:19" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="49" t="s">
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="49"/>
-      <c r="C4" s="49"/>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="49"/>
-      <c r="K4" s="49"/>
-    </row>
-    <row r="5" spans="1:16" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="50" t="s">
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+    </row>
+    <row r="5" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-    </row>
-    <row r="6" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="45" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+    </row>
+    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="46" t="s">
+      <c r="H6" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-    </row>
-    <row r="7" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="40" t="s">
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+    </row>
+    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="41" t="s">
+      <c r="H7" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
-      <c r="K7" s="41"/>
-    </row>
-    <row r="8" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>6</v>
       </c>
@@ -1183,7 +1197,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="188.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" ht="188.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>1</v>
       </c>
@@ -1200,7 +1214,7 @@
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="32" t="s">
         <v>30</v>
@@ -1209,11 +1223,11 @@
         <v>1</v>
       </c>
       <c r="D10" s="33">
-        <f>D34</f>
+        <f>D41</f>
         <v>5.5</v>
       </c>
       <c r="E10" s="33">
-        <f>F34/2</f>
+        <f>F41/2</f>
         <v>1.5</v>
       </c>
       <c r="F10" s="33">
@@ -1241,82 +1255,97 @@
         <v>160.09797821843054</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="16"/>
       <c r="B11" s="32"/>
       <c r="C11" s="17">
         <v>1</v>
       </c>
       <c r="D11" s="33">
-        <f>D35</f>
+        <f>D42</f>
         <v>13</v>
       </c>
       <c r="E11" s="33">
-        <f>F35/2</f>
-        <v>1.75</v>
+        <f>E18</f>
+        <v>1.5</v>
       </c>
       <c r="F11" s="33">
         <v>1</v>
       </c>
       <c r="G11" s="33">
         <f>PRODUCT(C11:F11)</f>
-        <v>22.75</v>
+        <v>19.5</v>
       </c>
       <c r="H11" s="17"/>
       <c r="I11" s="17"/>
       <c r="J11" s="17"/>
       <c r="K11" s="17"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-    </row>
-    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="34" t="s">
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="16"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="17">
+        <f>C19</f>
+        <v>1</v>
+      </c>
+      <c r="D12" s="33">
+        <f>D19</f>
+        <v>5</v>
+      </c>
+      <c r="E12" s="33">
+        <f>E19</f>
+        <v>1.075</v>
+      </c>
+      <c r="F12" s="33">
+        <v>0.6</v>
+      </c>
+      <c r="G12" s="33">
+        <f>PRODUCT(C12:F12)</f>
+        <v>3.2250000000000001</v>
+      </c>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+    </row>
+    <row r="13" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="6">
-        <f>SUM(G10:G11)</f>
-        <v>31</v>
-      </c>
-      <c r="H12" s="7" t="s">
+      <c r="C13" s="3"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="6">
+        <f>SUM(G10:G12)</f>
+        <v>30.975000000000001</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I13" s="6">
         <v>62.95</v>
       </c>
-      <c r="J12" s="18">
-        <f>G12*I12</f>
-        <v>1951.45</v>
-      </c>
-      <c r="K12" s="5"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A13" s="16"/>
-      <c r="B13" s="32" t="s">
+      <c r="J13" s="18">
+        <f>G13*I13</f>
+        <v>1949.8762500000003</v>
+      </c>
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A14" s="16"/>
+      <c r="B14" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="18">
-        <f>0.13*G12*(18612)/360</f>
-        <v>208.351</v>
-      </c>
-      <c r="K13" s="17"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="16"/>
-      <c r="B14" s="17"/>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
       <c r="E14" s="17"/>
@@ -1324,16 +1353,15 @@
       <c r="G14" s="17"/>
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
-      <c r="J14" s="17"/>
+      <c r="J14" s="18">
+        <f>0.13*G13*(18612)/360</f>
+        <v>208.18297500000003</v>
+      </c>
       <c r="K14" s="17"/>
     </row>
-    <row r="15" spans="1:16" ht="109.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="16">
-        <v>2</v>
-      </c>
-      <c r="B15" s="35" t="s">
-        <v>31</v>
-      </c>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" s="16"/>
+      <c r="B15" s="17"/>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
       <c r="E15" s="17"/>
@@ -1344,525 +1372,576 @@
       <c r="J15" s="17"/>
       <c r="K15" s="17"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="16"/>
-      <c r="B16" s="32" t="str">
-        <f>B10</f>
-        <v>-for masonary wall</v>
-      </c>
-      <c r="C16" s="17">
-        <v>1</v>
-      </c>
-      <c r="D16" s="33">
-        <f>D34</f>
-        <v>5.5</v>
-      </c>
-      <c r="E16" s="33">
-        <f>E10</f>
-        <v>1.5</v>
-      </c>
-      <c r="F16" s="33">
-        <v>0.15</v>
-      </c>
-      <c r="G16" s="33">
-        <f>PRODUCT(C16:F16)</f>
-        <v>1.2375</v>
-      </c>
+    <row r="16" spans="1:19" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="16">
+        <v>2</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
       <c r="K16" s="17"/>
-      <c r="M16" s="33">
-        <f>7</f>
-        <v>7</v>
-      </c>
-      <c r="N16" s="33">
-        <f>2</f>
-        <v>2</v>
-      </c>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33">
-        <f>PI()*M16*SQRT(M16^2+N16^2)</f>
-        <v>160.09797821843054</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R16" s="19">
+        <f>3/0.15</f>
+        <v>20</v>
+      </c>
+      <c r="S16" s="19">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
-      <c r="B17" s="32"/>
+      <c r="B17" s="32" t="str">
+        <f>B10</f>
+        <v>-for masonary wall</v>
+      </c>
       <c r="C17" s="17">
         <v>1</v>
       </c>
       <c r="D17" s="33">
-        <f>D35</f>
-        <v>13</v>
+        <f>D41</f>
+        <v>5.5</v>
       </c>
       <c r="E17" s="33">
-        <f>F35/2</f>
-        <v>1.75</v>
+        <f>E10</f>
+        <v>1.5</v>
       </c>
       <c r="F17" s="33">
         <v>0.15</v>
       </c>
       <c r="G17" s="33">
         <f>PRODUCT(C17:F17)</f>
-        <v>3.4125000000000001</v>
+        <v>1.2375</v>
       </c>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
       <c r="J17" s="17"/>
       <c r="K17" s="17"/>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-    </row>
-    <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="6">
-        <f>SUM(G16:G17)</f>
-        <v>4.6500000000000004</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I18" s="6">
-        <v>4458.5200000000004</v>
-      </c>
-      <c r="J18" s="18">
-        <f>G18*I18</f>
-        <v>20732.118000000002</v>
-      </c>
-      <c r="K18" s="5"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M17" s="33">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="N17" s="33">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="O17" s="33"/>
+      <c r="P17" s="33">
+        <f>PI()*M17*SQRT(M17^2+N17^2)</f>
+        <v>160.09797821843054</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="16"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="17">
+        <v>1</v>
+      </c>
+      <c r="D18" s="33">
+        <f>D42</f>
+        <v>13</v>
+      </c>
+      <c r="E18" s="33">
+        <f>E27</f>
+        <v>1.5</v>
+      </c>
+      <c r="F18" s="33">
+        <v>0.15</v>
+      </c>
+      <c r="G18" s="33">
+        <f>PRODUCT(C18:F18)</f>
+        <v>2.9249999999999998</v>
+      </c>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
-      <c r="B19" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="17">
+        <f>C29</f>
+        <v>1</v>
+      </c>
+      <c r="D19" s="33">
+        <f>D29</f>
+        <v>5</v>
+      </c>
+      <c r="E19" s="33">
+        <f>E29</f>
+        <v>1.075</v>
+      </c>
+      <c r="F19" s="33">
+        <v>0.15</v>
+      </c>
+      <c r="G19" s="33">
+        <f>PRODUCT(C19:F19)</f>
+        <v>0.80625000000000002</v>
+      </c>
       <c r="H19" s="17"/>
       <c r="I19" s="17"/>
-      <c r="J19" s="18">
-        <f>0.13*G18*(14817.6)/5</f>
-        <v>1791.44784</v>
-      </c>
+      <c r="J19" s="17"/>
       <c r="K19" s="17"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
+      <c r="B20" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="17">
+        <v>1</v>
+      </c>
+      <c r="D20" s="33">
+        <f>20*0.3</f>
+        <v>6</v>
+      </c>
+      <c r="E20" s="33">
+        <v>1.2</v>
+      </c>
+      <c r="F20" s="33">
+        <v>0.15</v>
+      </c>
+      <c r="G20" s="33">
+        <f>PRODUCT(C20:F20)</f>
+        <v>1.0799999999999998</v>
+      </c>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
       <c r="J20" s="17"/>
       <c r="K20" s="17"/>
-    </row>
-    <row r="21" spans="1:16" ht="93.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="16">
-        <v>3</v>
-      </c>
-      <c r="B21" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+    </row>
+    <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="6">
+        <f>SUM(G17:G20)</f>
+        <v>6.0487500000000001</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="6">
+        <v>4458.5200000000004</v>
+      </c>
+      <c r="J21" s="18">
+        <f>G21*I21</f>
+        <v>26968.472850000002</v>
+      </c>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
-      <c r="B22" s="32" t="str">
-        <f>B16</f>
-        <v>-for masonary wall</v>
-      </c>
-      <c r="C22" s="17">
-        <v>1</v>
-      </c>
-      <c r="D22" s="33">
-        <f>D34</f>
-        <v>5.5</v>
-      </c>
-      <c r="E22" s="33">
-        <f>E16</f>
-        <v>1.5</v>
-      </c>
-      <c r="F22" s="33">
-        <v>0.05</v>
-      </c>
-      <c r="G22" s="33">
-        <f>PRODUCT(C22:F22)</f>
-        <v>0.41250000000000003</v>
-      </c>
+      <c r="B22" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
       <c r="H22" s="17"/>
       <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
+      <c r="J22" s="18">
+        <f>0.13*G21*(14817.6)/5</f>
+        <v>2330.326908</v>
+      </c>
       <c r="K22" s="17"/>
-      <c r="M22" s="33">
-        <f>7</f>
-        <v>7</v>
-      </c>
-      <c r="N22" s="33">
-        <f>2</f>
-        <v>2</v>
-      </c>
-      <c r="O22" s="33"/>
-      <c r="P22" s="33">
-        <f>PI()*M22*SQRT(M22^2+N22^2)</f>
-        <v>160.09797821843054</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="16"/>
-      <c r="B23" s="32"/>
-      <c r="C23" s="17">
-        <v>1</v>
-      </c>
-      <c r="D23" s="33">
-        <f>D22</f>
-        <v>5.5</v>
-      </c>
-      <c r="E23" s="33">
-        <v>0.45</v>
-      </c>
-      <c r="F23" s="33">
-        <v>0.05</v>
-      </c>
-      <c r="G23" s="33">
-        <f>PRODUCT(C23:F23)</f>
-        <v>0.12375000000000001</v>
-      </c>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
       <c r="H23" s="17"/>
       <c r="I23" s="17"/>
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="36"/>
-      <c r="O23" s="36"/>
-      <c r="P23" s="36"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A24" s="16"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="17">
-        <v>1</v>
-      </c>
-      <c r="D24" s="33">
-        <f>D35</f>
-        <v>13</v>
-      </c>
-      <c r="E24" s="33">
-        <f>F35/2</f>
-        <v>1.75</v>
-      </c>
-      <c r="F24" s="33">
-        <v>0.05</v>
-      </c>
-      <c r="G24" s="33">
-        <f t="shared" ref="G24:G25" si="0">PRODUCT(C24:F24)</f>
-        <v>1.1375</v>
-      </c>
+    </row>
+    <row r="24" spans="1:16" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="16">
+        <v>3</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
       <c r="H24" s="17"/>
       <c r="I24" s="17"/>
       <c r="J24" s="17"/>
       <c r="K24" s="17"/>
-      <c r="M24" s="36"/>
-      <c r="N24" s="36"/>
-      <c r="O24" s="36"/>
-      <c r="P24" s="36"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="16"/>
-      <c r="B25" s="32"/>
+      <c r="B25" s="32" t="str">
+        <f>B17</f>
+        <v>-for masonary wall</v>
+      </c>
       <c r="C25" s="17">
         <v>1</v>
       </c>
       <c r="D25" s="33">
-        <f>D24</f>
-        <v>13</v>
+        <f>D41</f>
+        <v>5.5</v>
       </c>
       <c r="E25" s="33">
-        <v>0.45</v>
+        <f>E17</f>
+        <v>1.5</v>
       </c>
       <c r="F25" s="33">
         <v>0.05</v>
       </c>
       <c r="G25" s="33">
-        <f t="shared" si="0"/>
-        <v>0.29250000000000004</v>
+        <f>PRODUCT(C25:F25)</f>
+        <v>0.41250000000000003</v>
       </c>
       <c r="H25" s="17"/>
       <c r="I25" s="17"/>
       <c r="J25" s="17"/>
       <c r="K25" s="17"/>
-      <c r="M25" s="36"/>
-      <c r="N25" s="36"/>
-      <c r="O25" s="36"/>
-      <c r="P25" s="36"/>
-    </row>
-    <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="3"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="6">
-        <f>SUM(G22:G25)</f>
-        <v>1.9662500000000001</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I26" s="6">
-        <v>10964.46</v>
-      </c>
-      <c r="J26" s="18">
-        <f>G26*I26</f>
-        <v>21558.869475</v>
-      </c>
-      <c r="K26" s="5"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M25" s="33">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="N25" s="33">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33">
+        <f>PI()*M25*SQRT(M25^2+N25^2)</f>
+        <v>160.09797821843054</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="16"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="17">
+        <v>1</v>
+      </c>
+      <c r="D26" s="33">
+        <f>D25</f>
+        <v>5.5</v>
+      </c>
+      <c r="E26" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="F26" s="33">
+        <v>0.05</v>
+      </c>
+      <c r="G26" s="33">
+        <f>PRODUCT(C26:F26)</f>
+        <v>0.12375000000000001</v>
+      </c>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="M26" s="36"/>
+      <c r="N26" s="36"/>
+      <c r="O26" s="36"/>
+      <c r="P26" s="36"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="16"/>
-      <c r="B27" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="17">
+        <v>1</v>
+      </c>
+      <c r="D27" s="33">
+        <f>D42</f>
+        <v>13</v>
+      </c>
+      <c r="E27" s="33">
+        <f>3/2</f>
+        <v>1.5</v>
+      </c>
+      <c r="F27" s="33">
+        <v>0.05</v>
+      </c>
+      <c r="G27" s="33">
+        <f t="shared" ref="G27:G31" si="0">PRODUCT(C27:F27)</f>
+        <v>0.97500000000000009</v>
+      </c>
       <c r="H27" s="17"/>
       <c r="I27" s="17"/>
-      <c r="J27" s="18">
-        <f>0.13*G26*(53818.03)/15</f>
-        <v>917.10407955833341</v>
-      </c>
+      <c r="J27" s="17"/>
       <c r="K27" s="17"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M27" s="36"/>
+      <c r="N27" s="36"/>
+      <c r="O27" s="36"/>
+      <c r="P27" s="36"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
-      <c r="B28" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="17">
+        <v>1</v>
+      </c>
+      <c r="D28" s="33">
+        <f>D27</f>
+        <v>13</v>
+      </c>
+      <c r="E28" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="F28" s="33">
+        <v>0.05</v>
+      </c>
+      <c r="G28" s="33">
+        <f t="shared" si="0"/>
+        <v>0.29250000000000004</v>
+      </c>
       <c r="H28" s="17"/>
       <c r="I28" s="17"/>
-      <c r="J28" s="18">
-        <f>0.13*G26*(21432.6)/15</f>
-        <v>365.22936449999997</v>
-      </c>
+      <c r="J28" s="17"/>
       <c r="K28" s="17"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M28" s="36"/>
+      <c r="N28" s="36"/>
+      <c r="O28" s="36"/>
+      <c r="P28" s="36"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="16"/>
-      <c r="B29" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="17">
+        <f>C43</f>
+        <v>1</v>
+      </c>
+      <c r="D29" s="33">
+        <f>D43</f>
+        <v>5</v>
+      </c>
+      <c r="E29" s="33">
+        <f>F43/2</f>
+        <v>1.075</v>
+      </c>
+      <c r="F29" s="33">
+        <v>0.05</v>
+      </c>
+      <c r="G29" s="33">
+        <f t="shared" si="0"/>
+        <v>0.26874999999999999</v>
+      </c>
       <c r="H29" s="17"/>
       <c r="I29" s="17"/>
-      <c r="J29" s="18">
-        <f>0.13*G26*(25719.12+13573.98+4286.52)/15</f>
-        <v>742.63304115000005</v>
-      </c>
+      <c r="J29" s="17"/>
       <c r="K29" s="17"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M29" s="36"/>
+      <c r="N29" s="36"/>
+      <c r="O29" s="36"/>
+      <c r="P29" s="36"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="16"/>
-      <c r="B30" s="32" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="17">
+        <f>C29</f>
+        <v>1</v>
+      </c>
+      <c r="D30" s="33">
+        <f>D29</f>
+        <v>5</v>
+      </c>
+      <c r="E30" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="F30" s="33">
+        <v>0.05</v>
+      </c>
+      <c r="G30" s="33">
+        <f t="shared" si="0"/>
+        <v>0.1125</v>
+      </c>
       <c r="H30" s="17"/>
       <c r="I30" s="17"/>
-      <c r="J30" s="18">
-        <f>0.13*G26*(6325.7)/15</f>
-        <v>107.79519941666668</v>
-      </c>
+      <c r="J30" s="17"/>
       <c r="K30" s="17"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M30" s="36"/>
+      <c r="N30" s="36"/>
+      <c r="O30" s="36"/>
+      <c r="P30" s="36"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="16"/>
-      <c r="B31" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
+      <c r="B31" s="32" t="str">
+        <f>B20</f>
+        <v>-for steps</v>
+      </c>
+      <c r="C31" s="17">
+        <f>C20</f>
+        <v>1</v>
+      </c>
+      <c r="D31" s="33">
+        <f>D20</f>
+        <v>6</v>
+      </c>
+      <c r="E31" s="33">
+        <f>E20</f>
+        <v>1.2</v>
+      </c>
+      <c r="F31" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G31" s="33">
+        <f t="shared" si="0"/>
+        <v>0.53999999999999992</v>
+      </c>
       <c r="H31" s="17"/>
       <c r="I31" s="17"/>
-      <c r="J31" s="18">
-        <f>0.13*G26*(310)/5</f>
-        <v>15.847975000000002</v>
-      </c>
+      <c r="J31" s="17"/>
       <c r="K31" s="17"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M31" s="36"/>
+      <c r="N31" s="36"/>
+      <c r="O31" s="36"/>
+      <c r="P31" s="36"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="16"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="50">
+        <f>C44</f>
+        <v>0.5</v>
+      </c>
+      <c r="D32" s="33">
+        <f>D44</f>
+        <v>6</v>
+      </c>
+      <c r="E32" s="33">
+        <f>E44</f>
+        <v>0.5</v>
+      </c>
+      <c r="F32" s="33">
+        <v>0.05</v>
+      </c>
+      <c r="G32" s="33">
+        <f t="shared" ref="G32" si="1">PRODUCT(C32:F32)</f>
+        <v>7.5000000000000011E-2</v>
+      </c>
       <c r="H32" s="17"/>
       <c r="I32" s="17"/>
       <c r="J32" s="17"/>
       <c r="K32" s="17"/>
-    </row>
-    <row r="33" spans="1:19" ht="109.2" x14ac:dyDescent="0.3">
-      <c r="A33" s="16">
-        <v>4</v>
-      </c>
-      <c r="B33" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="M32" s="36"/>
+      <c r="N32" s="36"/>
+      <c r="O32" s="36"/>
+      <c r="P32" s="36"/>
+    </row>
+    <row r="33" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="6">
+        <f>SUM(G25:G32)</f>
+        <v>2.8</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="6">
+        <v>10964.46</v>
+      </c>
+      <c r="J33" s="18">
+        <f>G33*I33</f>
+        <v>30700.487999999994</v>
+      </c>
+      <c r="K33" s="5"/>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="16"/>
-      <c r="B34" s="32" t="str">
-        <f>B22</f>
-        <v>-for masonary wall</v>
-      </c>
-      <c r="C34" s="17">
-        <v>1</v>
-      </c>
-      <c r="D34" s="33">
-        <v>5.5</v>
-      </c>
-      <c r="E34" s="33">
-        <f>((F34/2)+0.45)/2</f>
-        <v>0.97499999999999998</v>
-      </c>
-      <c r="F34" s="33">
-        <v>3</v>
-      </c>
-      <c r="G34" s="33">
-        <f>PRODUCT(C34:F34)</f>
-        <v>16.087499999999999</v>
-      </c>
+      <c r="B34" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
       <c r="H34" s="17"/>
       <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
+      <c r="J34" s="18">
+        <f>0.13*G33*(53818.03)/15</f>
+        <v>1305.9841946666666</v>
+      </c>
       <c r="K34" s="17"/>
-      <c r="M34" s="33">
-        <f>7</f>
-        <v>7</v>
-      </c>
-      <c r="N34" s="33">
-        <f>2</f>
-        <v>2</v>
-      </c>
-      <c r="O34" s="33"/>
-      <c r="P34" s="33">
-        <f>PI()*M34*SQRT(M34^2+N34^2)</f>
-        <v>160.09797821843054</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="16"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="17">
-        <v>1</v>
-      </c>
-      <c r="D35" s="33">
-        <v>13</v>
-      </c>
-      <c r="E35" s="33">
-        <f>((F35/2)+0.45)/2</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F35" s="33">
-        <v>3.5</v>
-      </c>
-      <c r="G35" s="33">
-        <f>PRODUCT(C35:F35)</f>
-        <v>50.050000000000004</v>
-      </c>
+      <c r="B35" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
       <c r="H35" s="17"/>
       <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
+      <c r="J35" s="18">
+        <f>0.13*G33*(21432.6)/15</f>
+        <v>520.09775999999999</v>
+      </c>
       <c r="K35" s="17"/>
-      <c r="M35" s="37"/>
-      <c r="N35" s="37"/>
-      <c r="O35" s="37"/>
-      <c r="P35" s="37"/>
-    </row>
-    <row r="36" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2"/>
-      <c r="B36" s="34" t="s">
-        <v>17</v>
-      </c>
-      <c r="C36" s="3"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
-      <c r="G36" s="6">
-        <f>SUM(G34:G35)</f>
-        <v>66.137500000000003</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="I36" s="6">
-        <v>8987.83</v>
-      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" s="16"/>
+      <c r="B36" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
       <c r="J36" s="18">
-        <f>G36*I36</f>
-        <v>594432.60662500001</v>
-      </c>
-      <c r="K36" s="5"/>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+        <f>0.13*G33*(25719.12+13573.98+4286.52)/15</f>
+        <v>1057.5321119999999</v>
+      </c>
+      <c r="K36" s="17"/>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="16"/>
       <c r="B37" s="32" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
@@ -1872,15 +1951,15 @@
       <c r="H37" s="17"/>
       <c r="I37" s="17"/>
       <c r="J37" s="18">
-        <f>0.13*G36*(5863.95)/5</f>
-        <v>10083.50182125</v>
+        <f>0.13*G33*(6325.7)/15</f>
+        <v>153.50365333333332</v>
       </c>
       <c r="K37" s="17"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="16"/>
       <c r="B38" s="32" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C38" s="17"/>
       <c r="D38" s="17"/>
@@ -1890,16 +1969,14 @@
       <c r="H38" s="17"/>
       <c r="I38" s="17"/>
       <c r="J38" s="18">
-        <f>0.13*G36*(6604.416)/5</f>
-        <v>11356.7886432</v>
+        <f>0.13*G33*(310)/5</f>
+        <v>22.568000000000001</v>
       </c>
       <c r="K38" s="17"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="16"/>
-      <c r="B39" s="32" t="s">
-        <v>38</v>
-      </c>
+      <c r="B39" s="17"/>
       <c r="C39" s="17"/>
       <c r="D39" s="17"/>
       <c r="E39" s="17"/>
@@ -1907,16 +1984,15 @@
       <c r="G39" s="17"/>
       <c r="H39" s="17"/>
       <c r="I39" s="17"/>
-      <c r="J39" s="18">
-        <f>0.13*G36*(14808.78)/5</f>
-        <v>25464.8078685</v>
-      </c>
+      <c r="J39" s="17"/>
       <c r="K39" s="17"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A40" s="16"/>
-      <c r="B40" s="32" t="s">
-        <v>40</v>
+    <row r="40" spans="1:18" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A40" s="16">
+        <v>4</v>
+      </c>
+      <c r="B40" s="35" t="s">
+        <v>37</v>
       </c>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
@@ -1925,187 +2001,428 @@
       <c r="G40" s="17"/>
       <c r="H40" s="17"/>
       <c r="I40" s="17"/>
-      <c r="J40" s="18">
-        <f>0.13*G36*(310)/5</f>
-        <v>533.06825000000003</v>
-      </c>
+      <c r="J40" s="17"/>
       <c r="K40" s="17"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="16"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
+      <c r="B41" s="32" t="str">
+        <f>B25</f>
+        <v>-for masonary wall</v>
+      </c>
+      <c r="C41" s="17">
+        <v>1</v>
+      </c>
+      <c r="D41" s="33">
+        <v>5.5</v>
+      </c>
+      <c r="E41" s="33">
+        <f>((F41/2)+0.45)/2</f>
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="F41" s="33">
+        <v>3</v>
+      </c>
+      <c r="G41" s="33">
+        <f>PRODUCT(C41:F41)</f>
+        <v>16.087499999999999</v>
+      </c>
       <c r="H41" s="17"/>
       <c r="I41" s="17"/>
       <c r="J41" s="17"/>
       <c r="K41" s="17"/>
-    </row>
-    <row r="42" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
+      <c r="M41" s="33">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="N41" s="33">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="O41" s="33"/>
+      <c r="P41" s="33">
+        <f>PI()*M41*SQRT(M41^2+N41^2)</f>
+        <v>160.09797821843054</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" s="16"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="17">
+        <v>1</v>
+      </c>
+      <c r="D42" s="33">
+        <v>13</v>
+      </c>
+      <c r="E42" s="33">
+        <f>((F42/2)+(0.45))/2</f>
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="F42" s="33">
+        <v>3</v>
+      </c>
+      <c r="G42" s="33">
+        <f>PRODUCT(C42:F42)</f>
+        <v>38.024999999999999</v>
+      </c>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="M42" s="36"/>
+      <c r="N42" s="36"/>
+      <c r="O42" s="36"/>
+      <c r="P42" s="36"/>
+      <c r="Q42" s="19">
+        <f>E42*3.281</f>
+        <v>3.1989749999999999</v>
+      </c>
+      <c r="R42" s="19">
+        <f>F42*3.281</f>
+        <v>9.843</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" s="16"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="17">
+        <v>1</v>
+      </c>
+      <c r="D43" s="33">
         <v>5</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="E43" s="33">
+        <f>((F43/2)+0.45)/2</f>
+        <v>0.76249999999999996</v>
+      </c>
+      <c r="F43" s="33">
+        <v>2.15</v>
+      </c>
+      <c r="G43" s="33">
+        <f>PRODUCT(C43:F43)</f>
+        <v>8.1968750000000004</v>
+      </c>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="M43" s="36"/>
+      <c r="N43" s="36"/>
+      <c r="O43" s="36"/>
+      <c r="P43" s="36"/>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44" s="16"/>
+      <c r="B44" s="32" t="str">
+        <f>B31</f>
+        <v>-for steps</v>
+      </c>
+      <c r="C44" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="D44" s="33">
+        <f>0.3*20</f>
+        <v>6</v>
+      </c>
+      <c r="E44" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="F44" s="33">
+        <v>1.5</v>
+      </c>
+      <c r="G44" s="33">
+        <f>PRODUCT(C44:F44)</f>
+        <v>2.25</v>
+      </c>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="M44" s="36"/>
+      <c r="N44" s="36"/>
+      <c r="O44" s="36"/>
+      <c r="P44" s="36"/>
+    </row>
+    <row r="45" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2"/>
+      <c r="B45" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="6">
+        <f>SUM(G41:G44)</f>
+        <v>64.559374999999989</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="6">
+        <v>8987.83</v>
+      </c>
+      <c r="J45" s="18">
+        <f>G45*I45</f>
+        <v>580248.68740624993</v>
+      </c>
+      <c r="K45" s="5"/>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A46" s="16"/>
+      <c r="B46" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="18">
+        <f>0.13*G45*(5863.95)/5</f>
+        <v>9842.8966228124973</v>
+      </c>
+      <c r="K46" s="17"/>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47" s="16"/>
+      <c r="B47" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="18">
+        <f>0.13*G45*(6604.416)/5</f>
+        <v>11085.801199199999</v>
+      </c>
+      <c r="K47" s="17"/>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48" s="16"/>
+      <c r="B48" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="18">
+        <f>0.13*G45*(14808.78)/5</f>
+        <v>24857.185114124997</v>
+      </c>
+      <c r="K48" s="17"/>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A49" s="16"/>
+      <c r="B49" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="18">
+        <f>0.13*G45*(310)/5</f>
+        <v>520.34856249999996</v>
+      </c>
+      <c r="K49" s="17"/>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A50" s="16"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="17"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+    </row>
+    <row r="51" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>5</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C42" s="3">
-        <v>1</v>
-      </c>
-      <c r="D42" s="4"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="7">
-        <f t="shared" ref="G42" si="1">PRODUCT(C42:F42)</f>
-        <v>1</v>
-      </c>
-      <c r="H42" s="7" t="s">
+      <c r="C51" s="3">
+        <v>1</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="7">
+        <f t="shared" ref="G51" si="2">PRODUCT(C51:F51)</f>
+        <v>1</v>
+      </c>
+      <c r="H51" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I42" s="6">
+      <c r="I51" s="6">
         <v>500</v>
       </c>
-      <c r="J42" s="7">
-        <f>G42*I42</f>
+      <c r="J51" s="7">
+        <f>G51*I51</f>
         <v>500</v>
       </c>
-      <c r="K42" s="5"/>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A43" s="2"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="3"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="18"/>
-      <c r="K43" s="5"/>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A44" s="21"/>
-      <c r="B44" s="22" t="s">
+      <c r="K51" s="5"/>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A52" s="2"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="5"/>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A53" s="21"/>
+      <c r="B53" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C44" s="23"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="24"/>
-      <c r="F44" s="24"/>
-      <c r="G44" s="18"/>
-      <c r="H44" s="18"/>
-      <c r="I44" s="18"/>
-      <c r="J44" s="18">
-        <f>SUM(J9:J42)</f>
-        <v>690761.61918257491</v>
-      </c>
-      <c r="K44" s="25"/>
-    </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="M45" s="20"/>
-      <c r="N45" s="20"/>
-      <c r="O45" s="20"/>
-      <c r="P45" s="20"/>
-      <c r="Q45" s="20"/>
-      <c r="R45" s="20"/>
-      <c r="S45" s="20"/>
-    </row>
-    <row r="46" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="26"/>
-      <c r="B46" s="27" t="s">
+      <c r="C53" s="23"/>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="18">
+        <f>SUM(J9:J51)</f>
+        <v>692271.9516078874</v>
+      </c>
+      <c r="K53" s="25"/>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="M54" s="20"/>
+      <c r="N54" s="20"/>
+      <c r="O54" s="20"/>
+      <c r="P54" s="20"/>
+      <c r="Q54" s="20"/>
+      <c r="R54" s="20"/>
+      <c r="S54" s="20"/>
+    </row>
+    <row r="55" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="26"/>
+      <c r="B55" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C46" s="38">
-        <f>J44</f>
-        <v>690761.61918257491</v>
-      </c>
-      <c r="D46" s="39"/>
-      <c r="E46" s="9">
+      <c r="C55" s="43">
+        <f>J53</f>
+        <v>692271.9516078874</v>
+      </c>
+      <c r="D55" s="44"/>
+      <c r="E55" s="9">
         <v>100</v>
       </c>
-      <c r="F46" s="26"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="26"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="31"/>
-      <c r="M46" s="19"/>
-      <c r="N46" s="19"/>
-      <c r="O46" s="19"/>
-      <c r="P46" s="19"/>
-      <c r="Q46" s="19"/>
-      <c r="R46" s="19"/>
-      <c r="S46" s="19"/>
-    </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B47" s="27" t="s">
+      <c r="F55" s="26"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="26"/>
+      <c r="I55" s="29"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="31"/>
+      <c r="M55" s="19"/>
+      <c r="N55" s="19"/>
+      <c r="O55" s="19"/>
+      <c r="P55" s="19"/>
+      <c r="Q55" s="19"/>
+      <c r="R55" s="19"/>
+      <c r="S55" s="19"/>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B56" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C47" s="42">
+      <c r="C56" s="47">
         <v>600000</v>
       </c>
-      <c r="D47" s="43"/>
-      <c r="E47" s="9"/>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="B48" s="27" t="s">
+      <c r="D56" s="48"/>
+      <c r="E56" s="9"/>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B57" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="C48" s="42">
-        <f>C47-C50-C51</f>
+      <c r="C57" s="47">
+        <f>C56-C59-C60</f>
         <v>570000</v>
       </c>
-      <c r="D48" s="43"/>
-      <c r="E48" s="9">
-        <f>C48/C46*100</f>
-        <v>82.51761304782967</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B49" s="27" t="s">
+      <c r="D57" s="48"/>
+      <c r="E57" s="9">
+        <f>C57/C55*100</f>
+        <v>82.337584048595986</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B58" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="44">
-        <f>C46-C48</f>
-        <v>120761.61918257491</v>
-      </c>
-      <c r="D49" s="44"/>
-      <c r="E49" s="9">
-        <f>100-E48</f>
-        <v>17.48238695217033</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B50" s="27" t="s">
+      <c r="C58" s="49">
+        <f>C55-C57</f>
+        <v>122271.9516078874</v>
+      </c>
+      <c r="D58" s="49"/>
+      <c r="E58" s="9">
+        <f>100-E57</f>
+        <v>17.662415951404014</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B59" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C50" s="38">
-        <f>C47*0.03</f>
+      <c r="C59" s="43">
+        <f>C56*0.03</f>
         <v>18000</v>
       </c>
-      <c r="D50" s="39"/>
-      <c r="E50" s="9">
+      <c r="D59" s="44"/>
+      <c r="E59" s="9">
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B51" s="27" t="s">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B60" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="C51" s="38">
-        <f>C47*0.02</f>
+      <c r="C60" s="43">
+        <f>C56*0.02</f>
         <v>12000</v>
       </c>
-      <c r="D51" s="39"/>
-      <c r="E51" s="9">
+      <c r="D60" s="44"/>
+      <c r="E60" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C58:D58"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="A1:K1"/>
@@ -2113,14 +2430,6 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C49:D49"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -2128,7 +2437,1416 @@
     <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="32" max="10" man="1"/>
+    <brk id="39" max="10" man="1"/>
+  </rowBreaks>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BA1FB56-BF34-46CB-8637-C502539815AC}">
+  <dimension ref="A1:S60"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="19" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="19" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="19"/>
+    <col min="8" max="8" width="5" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" style="19" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="19" hidden="1" customWidth="1"/>
+    <col min="11" max="12" width="9.140625" style="19"/>
+    <col min="13" max="16" width="0" style="19" hidden="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+    </row>
+    <row r="2" spans="1:19" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" s="41" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+    </row>
+    <row r="5" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+    </row>
+    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="37"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+    </row>
+    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="45" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="188.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="16">
+        <v>1</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="16"/>
+      <c r="B10" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="17">
+        <v>1</v>
+      </c>
+      <c r="D10" s="33">
+        <f>D41</f>
+        <v>5.5</v>
+      </c>
+      <c r="E10" s="33">
+        <f>F41/2</f>
+        <v>1.5</v>
+      </c>
+      <c r="F10" s="33">
+        <v>1</v>
+      </c>
+      <c r="G10" s="33">
+        <f>PRODUCT(C10:F10)</f>
+        <v>8.25</v>
+      </c>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="M10" s="33">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="N10" s="33">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="O10" s="33"/>
+      <c r="P10" s="33">
+        <f>PI()*M10*SQRT(M10^2+N10^2)</f>
+        <v>160.09797821843054</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="16"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="17">
+        <v>1</v>
+      </c>
+      <c r="D11" s="33">
+        <f>D42</f>
+        <v>13</v>
+      </c>
+      <c r="E11" s="33">
+        <f>E18</f>
+        <v>1.5</v>
+      </c>
+      <c r="F11" s="33">
+        <v>1</v>
+      </c>
+      <c r="G11" s="33">
+        <f>PRODUCT(C11:F11)</f>
+        <v>19.5</v>
+      </c>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A12" s="16"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="17">
+        <f>C19</f>
+        <v>1</v>
+      </c>
+      <c r="D12" s="33">
+        <f>D19</f>
+        <v>5</v>
+      </c>
+      <c r="E12" s="33">
+        <f>E19</f>
+        <v>1.075</v>
+      </c>
+      <c r="F12" s="33">
+        <v>0.6</v>
+      </c>
+      <c r="G12" s="33">
+        <f>PRODUCT(C12:F12)</f>
+        <v>3.2250000000000001</v>
+      </c>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+    </row>
+    <row r="13" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="B13" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="6">
+        <f>SUM(G10:G12)</f>
+        <v>30.975000000000001</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="6">
+        <v>62.95</v>
+      </c>
+      <c r="J13" s="18">
+        <f>G13*I13</f>
+        <v>1949.8762500000003</v>
+      </c>
+      <c r="K13" s="5"/>
+    </row>
+    <row r="14" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="16"/>
+      <c r="B14" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="18">
+        <f>0.13*G13*(18612)/360</f>
+        <v>208.18297500000003</v>
+      </c>
+      <c r="K14" s="17"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A15" s="16"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+    </row>
+    <row r="16" spans="1:19" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="16">
+        <v>2</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="17"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+      <c r="K16" s="17"/>
+      <c r="R16" s="19">
+        <f>3/0.15</f>
+        <v>20</v>
+      </c>
+      <c r="S16" s="19">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A17" s="16"/>
+      <c r="B17" s="32" t="str">
+        <f>B10</f>
+        <v>-for masonary wall</v>
+      </c>
+      <c r="C17" s="17">
+        <v>1</v>
+      </c>
+      <c r="D17" s="33">
+        <f>D41</f>
+        <v>5.5</v>
+      </c>
+      <c r="E17" s="33">
+        <f>E10</f>
+        <v>1.5</v>
+      </c>
+      <c r="F17" s="33">
+        <v>0.15</v>
+      </c>
+      <c r="G17" s="33">
+        <f>PRODUCT(C17:F17)</f>
+        <v>1.2375</v>
+      </c>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="M17" s="33">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="N17" s="33">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="O17" s="33"/>
+      <c r="P17" s="33">
+        <f>PI()*M17*SQRT(M17^2+N17^2)</f>
+        <v>160.09797821843054</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="16"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="17">
+        <v>1</v>
+      </c>
+      <c r="D18" s="33">
+        <f>D42</f>
+        <v>13</v>
+      </c>
+      <c r="E18" s="33">
+        <f>E27</f>
+        <v>1.5</v>
+      </c>
+      <c r="F18" s="33">
+        <v>0.15</v>
+      </c>
+      <c r="G18" s="33">
+        <f>PRODUCT(C18:F18)</f>
+        <v>2.9249999999999998</v>
+      </c>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17"/>
+      <c r="K18" s="17"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="16"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="17">
+        <f>C29</f>
+        <v>1</v>
+      </c>
+      <c r="D19" s="33">
+        <f>D29</f>
+        <v>5</v>
+      </c>
+      <c r="E19" s="33">
+        <f>E29</f>
+        <v>1.075</v>
+      </c>
+      <c r="F19" s="33">
+        <v>0.15</v>
+      </c>
+      <c r="G19" s="33">
+        <f>PRODUCT(C19:F19)</f>
+        <v>0.80625000000000002</v>
+      </c>
+      <c r="H19" s="17"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A20" s="16"/>
+      <c r="B20" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="17">
+        <v>1</v>
+      </c>
+      <c r="D20" s="33">
+        <f>20*0.3</f>
+        <v>6</v>
+      </c>
+      <c r="E20" s="33">
+        <v>1.2</v>
+      </c>
+      <c r="F20" s="33">
+        <v>0.15</v>
+      </c>
+      <c r="G20" s="33">
+        <f>PRODUCT(C20:F20)</f>
+        <v>1.0799999999999998</v>
+      </c>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17"/>
+      <c r="K20" s="17"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+    </row>
+    <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="3"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="6">
+        <f>SUM(G17:G20)</f>
+        <v>6.0487500000000001</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="6">
+        <v>4458.5200000000004</v>
+      </c>
+      <c r="J21" s="18">
+        <f>G21*I21</f>
+        <v>26968.472850000002</v>
+      </c>
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="16"/>
+      <c r="B22" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="18">
+        <f>0.13*G21*(14817.6)/5</f>
+        <v>2330.326908</v>
+      </c>
+      <c r="K22" s="17"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A23" s="16"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+    </row>
+    <row r="24" spans="1:16" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="16">
+        <v>3</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+      <c r="K24" s="17"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="16"/>
+      <c r="B25" s="32" t="str">
+        <f>B17</f>
+        <v>-for masonary wall</v>
+      </c>
+      <c r="C25" s="17">
+        <v>1</v>
+      </c>
+      <c r="D25" s="33">
+        <f>D41</f>
+        <v>5.5</v>
+      </c>
+      <c r="E25" s="33">
+        <f>E17</f>
+        <v>1.5</v>
+      </c>
+      <c r="F25" s="33">
+        <v>0.05</v>
+      </c>
+      <c r="G25" s="33">
+        <f>PRODUCT(C25:F25)</f>
+        <v>0.41250000000000003</v>
+      </c>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="M25" s="33">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="N25" s="33">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33">
+        <f>PI()*M25*SQRT(M25^2+N25^2)</f>
+        <v>160.09797821843054</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="16"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="17">
+        <v>1</v>
+      </c>
+      <c r="D26" s="33">
+        <f>D25</f>
+        <v>5.5</v>
+      </c>
+      <c r="E26" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="F26" s="33">
+        <v>0.05</v>
+      </c>
+      <c r="G26" s="33">
+        <f>PRODUCT(C26:F26)</f>
+        <v>0.12375000000000001</v>
+      </c>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+      <c r="K26" s="17"/>
+      <c r="M26" s="36"/>
+      <c r="N26" s="36"/>
+      <c r="O26" s="36"/>
+      <c r="P26" s="36"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="16"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="17">
+        <v>1</v>
+      </c>
+      <c r="D27" s="33">
+        <f>D42</f>
+        <v>13</v>
+      </c>
+      <c r="E27" s="33">
+        <f>3/2</f>
+        <v>1.5</v>
+      </c>
+      <c r="F27" s="33">
+        <v>0.05</v>
+      </c>
+      <c r="G27" s="33">
+        <f t="shared" ref="G27:G32" si="0">PRODUCT(C27:F27)</f>
+        <v>0.97500000000000009</v>
+      </c>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="M27" s="36"/>
+      <c r="N27" s="36"/>
+      <c r="O27" s="36"/>
+      <c r="P27" s="36"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="16"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="17">
+        <v>1</v>
+      </c>
+      <c r="D28" s="33">
+        <f>D27</f>
+        <v>13</v>
+      </c>
+      <c r="E28" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="F28" s="33">
+        <v>0.05</v>
+      </c>
+      <c r="G28" s="33">
+        <f t="shared" si="0"/>
+        <v>0.29250000000000004</v>
+      </c>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+      <c r="K28" s="17"/>
+      <c r="M28" s="36"/>
+      <c r="N28" s="36"/>
+      <c r="O28" s="36"/>
+      <c r="P28" s="36"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="16"/>
+      <c r="B29" s="32"/>
+      <c r="C29" s="17">
+        <f>C43</f>
+        <v>1</v>
+      </c>
+      <c r="D29" s="33">
+        <f>D43</f>
+        <v>5</v>
+      </c>
+      <c r="E29" s="33">
+        <f>F43/2</f>
+        <v>1.075</v>
+      </c>
+      <c r="F29" s="33">
+        <v>0.05</v>
+      </c>
+      <c r="G29" s="33">
+        <f t="shared" si="0"/>
+        <v>0.26874999999999999</v>
+      </c>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="M29" s="36"/>
+      <c r="N29" s="36"/>
+      <c r="O29" s="36"/>
+      <c r="P29" s="36"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="16"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="17">
+        <f>C29</f>
+        <v>1</v>
+      </c>
+      <c r="D30" s="33">
+        <f>D29</f>
+        <v>5</v>
+      </c>
+      <c r="E30" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="F30" s="33">
+        <v>0.05</v>
+      </c>
+      <c r="G30" s="33">
+        <f t="shared" si="0"/>
+        <v>0.1125</v>
+      </c>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="36"/>
+      <c r="O30" s="36"/>
+      <c r="P30" s="36"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="16"/>
+      <c r="B31" s="32" t="str">
+        <f>B20</f>
+        <v>-for steps</v>
+      </c>
+      <c r="C31" s="17">
+        <f>C20</f>
+        <v>1</v>
+      </c>
+      <c r="D31" s="33">
+        <f>D20</f>
+        <v>6</v>
+      </c>
+      <c r="E31" s="33">
+        <f>E20</f>
+        <v>1.2</v>
+      </c>
+      <c r="F31" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G31" s="33">
+        <f t="shared" si="0"/>
+        <v>0.53999999999999992</v>
+      </c>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
+      <c r="M31" s="36"/>
+      <c r="N31" s="36"/>
+      <c r="O31" s="36"/>
+      <c r="P31" s="36"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="16"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="50">
+        <f>C44</f>
+        <v>0.5</v>
+      </c>
+      <c r="D32" s="33">
+        <f>D44</f>
+        <v>6</v>
+      </c>
+      <c r="E32" s="33">
+        <f>E44</f>
+        <v>0.5</v>
+      </c>
+      <c r="F32" s="33">
+        <v>0.05</v>
+      </c>
+      <c r="G32" s="33">
+        <f t="shared" si="0"/>
+        <v>7.5000000000000011E-2</v>
+      </c>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
+      <c r="M32" s="36"/>
+      <c r="N32" s="36"/>
+      <c r="O32" s="36"/>
+      <c r="P32" s="36"/>
+    </row>
+    <row r="33" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="6">
+        <f>SUM(G25:G32)</f>
+        <v>2.8</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="6">
+        <v>10964.46</v>
+      </c>
+      <c r="J33" s="18">
+        <f>G33*I33</f>
+        <v>30700.487999999994</v>
+      </c>
+      <c r="K33" s="5"/>
+    </row>
+    <row r="34" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="16"/>
+      <c r="B34" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" s="17"/>
+      <c r="D34" s="17"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="18">
+        <f>0.13*G33*(53818.03)/15</f>
+        <v>1305.9841946666666</v>
+      </c>
+      <c r="K34" s="17"/>
+    </row>
+    <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="16"/>
+      <c r="B35" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="18">
+        <f>0.13*G33*(21432.6)/15</f>
+        <v>520.09775999999999</v>
+      </c>
+      <c r="K35" s="17"/>
+    </row>
+    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="16"/>
+      <c r="B36" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="18">
+        <f>0.13*G33*(25719.12+13573.98+4286.52)/15</f>
+        <v>1057.5321119999999</v>
+      </c>
+      <c r="K36" s="17"/>
+    </row>
+    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="16"/>
+      <c r="B37" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="17"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="18">
+        <f>0.13*G33*(6325.7)/15</f>
+        <v>153.50365333333332</v>
+      </c>
+      <c r="K37" s="17"/>
+    </row>
+    <row r="38" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="16"/>
+      <c r="B38" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="17"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="17"/>
+      <c r="J38" s="18">
+        <f>0.13*G33*(310)/5</f>
+        <v>22.568000000000001</v>
+      </c>
+      <c r="K38" s="17"/>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A39" s="16"/>
+      <c r="B39" s="17"/>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
+    </row>
+    <row r="40" spans="1:18" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A40" s="16">
+        <v>4</v>
+      </c>
+      <c r="B40" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A41" s="16"/>
+      <c r="B41" s="32" t="str">
+        <f>B25</f>
+        <v>-for masonary wall</v>
+      </c>
+      <c r="C41" s="17">
+        <v>1</v>
+      </c>
+      <c r="D41" s="33">
+        <v>5.5</v>
+      </c>
+      <c r="E41" s="33">
+        <f>((F41/2)+0.45)/2</f>
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="F41" s="33">
+        <v>3</v>
+      </c>
+      <c r="G41" s="33">
+        <f>PRODUCT(C41:F41)</f>
+        <v>16.087499999999999</v>
+      </c>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="M41" s="33">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="N41" s="33">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="O41" s="33"/>
+      <c r="P41" s="33">
+        <f>PI()*M41*SQRT(M41^2+N41^2)</f>
+        <v>160.09797821843054</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A42" s="16"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="17">
+        <v>1</v>
+      </c>
+      <c r="D42" s="33">
+        <v>13</v>
+      </c>
+      <c r="E42" s="33">
+        <f>((F42/2)+(0.45))/2</f>
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="F42" s="33">
+        <v>3</v>
+      </c>
+      <c r="G42" s="33">
+        <f>PRODUCT(C42:F42)</f>
+        <v>38.024999999999999</v>
+      </c>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
+      <c r="M42" s="36"/>
+      <c r="N42" s="36"/>
+      <c r="O42" s="36"/>
+      <c r="P42" s="36"/>
+      <c r="Q42" s="19">
+        <f>E42*3.281</f>
+        <v>3.1989749999999999</v>
+      </c>
+      <c r="R42" s="19">
+        <f>F42*3.281</f>
+        <v>9.843</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" s="16"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="17">
+        <v>1</v>
+      </c>
+      <c r="D43" s="33">
+        <v>5</v>
+      </c>
+      <c r="E43" s="33">
+        <f>((F43/2)+0.45)/2</f>
+        <v>0.76249999999999996</v>
+      </c>
+      <c r="F43" s="33">
+        <v>2.15</v>
+      </c>
+      <c r="G43" s="33">
+        <f>PRODUCT(C43:F43)</f>
+        <v>8.1968750000000004</v>
+      </c>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
+      <c r="M43" s="36"/>
+      <c r="N43" s="36"/>
+      <c r="O43" s="36"/>
+      <c r="P43" s="36"/>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A44" s="16"/>
+      <c r="B44" s="32" t="str">
+        <f>B31</f>
+        <v>-for steps</v>
+      </c>
+      <c r="C44" s="50">
+        <v>0.5</v>
+      </c>
+      <c r="D44" s="33">
+        <f>0.3*20</f>
+        <v>6</v>
+      </c>
+      <c r="E44" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="F44" s="33">
+        <v>1.5</v>
+      </c>
+      <c r="G44" s="33">
+        <f>PRODUCT(C44:F44)</f>
+        <v>2.25</v>
+      </c>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="M44" s="36"/>
+      <c r="N44" s="36"/>
+      <c r="O44" s="36"/>
+      <c r="P44" s="36"/>
+    </row>
+    <row r="45" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2"/>
+      <c r="B45" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="6">
+        <f>SUM(G41:G44)</f>
+        <v>64.559374999999989</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I45" s="6">
+        <v>8987.83</v>
+      </c>
+      <c r="J45" s="18">
+        <f>G45*I45</f>
+        <v>580248.68740624993</v>
+      </c>
+      <c r="K45" s="5"/>
+    </row>
+    <row r="46" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="16"/>
+      <c r="B46" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C46" s="17"/>
+      <c r="D46" s="17"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="18">
+        <f>0.13*G45*(5863.95)/5</f>
+        <v>9842.8966228124973</v>
+      </c>
+      <c r="K46" s="17"/>
+    </row>
+    <row r="47" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="16"/>
+      <c r="B47" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47" s="17"/>
+      <c r="D47" s="17"/>
+      <c r="E47" s="17"/>
+      <c r="F47" s="17"/>
+      <c r="G47" s="17"/>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="18">
+        <f>0.13*G45*(6604.416)/5</f>
+        <v>11085.801199199999</v>
+      </c>
+      <c r="K47" s="17"/>
+    </row>
+    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="16"/>
+      <c r="B48" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="18">
+        <f>0.13*G45*(14808.78)/5</f>
+        <v>24857.185114124997</v>
+      </c>
+      <c r="K48" s="17"/>
+    </row>
+    <row r="49" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="16"/>
+      <c r="B49" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="18">
+        <f>0.13*G45*(310)/5</f>
+        <v>520.34856249999996</v>
+      </c>
+      <c r="K49" s="17"/>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A50" s="16"/>
+      <c r="B50" s="17"/>
+      <c r="C50" s="17"/>
+      <c r="D50" s="17"/>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="17"/>
+      <c r="H50" s="17"/>
+      <c r="I50" s="17"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+    </row>
+    <row r="51" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>5</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C51" s="3">
+        <v>1</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="7">
+        <f t="shared" ref="G51" si="1">PRODUCT(C51:F51)</f>
+        <v>1</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" s="6">
+        <v>500</v>
+      </c>
+      <c r="J51" s="7">
+        <f>G51*I51</f>
+        <v>500</v>
+      </c>
+      <c r="K51" s="5"/>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A52" s="2"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="7"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="5"/>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A53" s="21"/>
+      <c r="B53" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C53" s="23"/>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="18"/>
+      <c r="I53" s="18"/>
+      <c r="J53" s="18">
+        <f>SUM(J9:J51)</f>
+        <v>692271.9516078874</v>
+      </c>
+      <c r="K53" s="25"/>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="M54" s="20"/>
+      <c r="N54" s="20"/>
+      <c r="O54" s="20"/>
+      <c r="P54" s="20"/>
+      <c r="Q54" s="20"/>
+      <c r="R54" s="20"/>
+      <c r="S54" s="20"/>
+    </row>
+    <row r="55" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="26"/>
+      <c r="B55" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C55" s="43">
+        <f>J53</f>
+        <v>692271.9516078874</v>
+      </c>
+      <c r="D55" s="44"/>
+      <c r="E55" s="9">
+        <v>100</v>
+      </c>
+      <c r="F55" s="26"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="26"/>
+      <c r="I55" s="29"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="31"/>
+      <c r="M55" s="19"/>
+      <c r="N55" s="19"/>
+      <c r="O55" s="19"/>
+      <c r="P55" s="19"/>
+      <c r="Q55" s="19"/>
+      <c r="R55" s="19"/>
+      <c r="S55" s="19"/>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B56" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C56" s="47">
+        <v>600000</v>
+      </c>
+      <c r="D56" s="48"/>
+      <c r="E56" s="9"/>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B57" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" s="47">
+        <f>C56-C59-C60</f>
+        <v>570000</v>
+      </c>
+      <c r="D57" s="48"/>
+      <c r="E57" s="9">
+        <f>C57/C55*100</f>
+        <v>82.337584048595986</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B58" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C58" s="49">
+        <f>C55-C57</f>
+        <v>122271.9516078874</v>
+      </c>
+      <c r="D58" s="49"/>
+      <c r="E58" s="9">
+        <f>100-E57</f>
+        <v>17.662415951404014</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B59" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C59" s="43">
+        <f>C56*0.03</f>
+        <v>18000</v>
+      </c>
+      <c r="D59" s="44"/>
+      <c r="E59" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B60" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C60" s="43">
+        <f>C56*0.02</f>
+        <v>12000</v>
+      </c>
+      <c r="D60" s="44"/>
+      <c r="E60" s="9">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+  </mergeCells>
+  <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
+  </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="39" max="10" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>